--- a/outputs/daily/hr_rankings_2026-09-13_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-13_full.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6082,17 +6082,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -6110,26 +6110,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.6</v>
+        <v>55.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.1</v>
+        <v>37.6</v>
       </c>
       <c r="R21" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>43.7</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6181,142 +6181,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.8043</t>
+          <t>102.6789</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3856</t>
+          <t>0.4845</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.2296</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3155</t>
+          <t>0.3692</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>68.45</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2264</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1576</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6327,27 +6327,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-13T19:05:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6362,21 +6362,21 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6390,26 +6390,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>55.9</v>
+        <v>35.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.6</v>
+        <v>42.1</v>
       </c>
       <c r="R22" t="n">
-        <v>31.2</v>
+        <v>52.9</v>
       </c>
       <c r="S22" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>43.7</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6461,142 +6461,142 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>102.6789</t>
+          <t>101.8043</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4845</t>
+          <t>0.3856</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.2296</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3692</t>
+          <t>0.3155</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>73.63</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68.45</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.2264</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1576</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -8287,27 +8287,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8317,26 +8317,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8350,26 +8350,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>39.6</v>
+        <v>47</v>
       </c>
       <c r="Q29" t="n">
-        <v>42.1</v>
+        <v>29.2</v>
       </c>
       <c r="R29" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S29" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>19.1</v>
+        <v>50.3</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -8436,127 +8436,127 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>99.8028</t>
+          <t>100.7907</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.4619</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.2799</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1701</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.3497</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8567,27 +8567,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-13T19:05:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8597,22 +8597,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -8630,26 +8630,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>47</v>
+        <v>39.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.2</v>
+        <v>42.1</v>
       </c>
       <c r="R30" t="n">
-        <v>31.2</v>
+        <v>52.9</v>
       </c>
       <c r="S30" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>50.3</v>
+        <v>18.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8716,127 +8716,127 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>100.7907</t>
+          <t>99.8028</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4619</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.1732</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.2799</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.22</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1701</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3497</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9683,27 +9683,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9713,22 +9713,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -9746,26 +9746,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="R34" t="n">
-        <v>52.9</v>
+        <v>44.2</v>
       </c>
       <c r="S34" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U34" t="n">
-        <v>52.8</v>
+        <v>24</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9822,137 +9822,137 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.0298</t>
+          <t>100.4107</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4273</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2845</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>37.69</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1608</t>
+          <t>0.1432</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>33.66</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9963,27 +9963,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-13T20:10:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9993,26 +9993,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10026,26 +10026,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>37.1</v>
+        <v>42.1</v>
       </c>
       <c r="R35" t="n">
-        <v>44.2</v>
+        <v>52.9</v>
       </c>
       <c r="S35" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>24</v>
+        <v>50.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10102,137 +10102,137 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.4107</t>
+          <t>101.0298</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4273</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3341</t>
+          <t>0.2845</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1432</t>
+          <t>0.1608</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>75</v>
       </c>
       <c r="U42" t="n">
-        <v>77.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14237,7 +14237,7 @@
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20057,7 +20057,7 @@
         <v>75</v>
       </c>
       <c r="U71" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23470,7 +23470,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/8, 0 HR</t>
+          <t>Last 7 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -31493,27 +31493,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -31528,17 +31528,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -31556,26 +31556,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.6</v>
+        <v>55.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.1</v>
+        <v>37.6</v>
       </c>
       <c r="R21" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>43.7</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -31627,142 +31627,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.8043</t>
+          <t>102.6789</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3856</t>
+          <t>0.4845</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.2296</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3155</t>
+          <t>0.3692</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>68.45</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2264</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1576</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
